--- a/data/trans_bre/P15B_tráfico-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P15B_tráfico-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-31,31</t>
+          <t>-27,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-65,87%</t>
+          <t>-65,26%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 55,31</t>
+          <t>-29,94; 56,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 6,43</t>
+          <t>-42,9; 8,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 19,02</t>
+          <t>-34,88; 18,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-57,27; -6,63</t>
+          <t>-51,74; -6,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 25,21</t>
+          <t>-76,22; 23,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 152,37</t>
+          <t>-74,42; 134,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,3; -20,67</t>
+          <t>-86,68; -20,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-18,39</t>
+          <t>-15,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-52,23%</t>
+          <t>-45,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-86,74; -3,17</t>
+          <t>-85,97; 3,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 5,0</t>
+          <t>-40,43; 3,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 38,42</t>
+          <t>-16,88; 41,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 7,14</t>
+          <t>-41,19; 9,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,04; -5,43</t>
+          <t>-89,13; 1,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,44; 23,61</t>
+          <t>-81,87; 14,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,37; 712,67</t>
+          <t>-79,43; 805,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,04; 96,89</t>
+          <t>-81,8; 77,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-60,55; -14,69</t>
+          <t>-63,4; -13,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 20,3</t>
+          <t>-6,18; 21,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 11,51</t>
+          <t>-32,6; 14,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 22,55</t>
+          <t>-11,35; 24,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,21; 844,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,33</t>
+          <t>-100,0; 206,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-83,1; —</t>
+          <t>-77,67; —</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,18</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>110,57%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 61,15</t>
+          <t>-7,16; 59,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,63; -0,25</t>
+          <t>-40,77; 1,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,51; -9,44</t>
+          <t>-35,14; -7,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 60,59</t>
+          <t>-19,75; 56,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 237,95</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,08; 782,32</t>
+          <t>-54,92; 465,57</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-20,27</t>
+          <t>-21,89</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 55,84</t>
+          <t>-26,08; 53,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 48,46</t>
+          <t>-20,22; 47,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 0,0</t>
+          <t>-46,39; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,35; 523,55</t>
+          <t>-46,5; 372,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,21</t>
+          <t>-5,59</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-51,04%</t>
+          <t>-49,18%</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 3,63</t>
+          <t>-36,12; 4,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 12,69</t>
+          <t>-21,06; 14,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 4,85</t>
+          <t>-21,31; 4,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,1; 46,83</t>
+          <t>-88,55; 42,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-13,06</t>
+          <t>-15,25</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-39,09%</t>
+          <t>-43,23%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 20,37</t>
+          <t>-32,55; 19,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 15,53</t>
+          <t>-8,72; 16,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 36,79</t>
+          <t>-20,02; 35,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 6,76</t>
+          <t>-32,85; 2,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-81,07; 147,72</t>
+          <t>-83,28; 142,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-52,87; 190,92</t>
+          <t>-48,06; 226,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 268,64</t>
+          <t>-49,7; 221,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 42,68</t>
+          <t>-72,81; 18,76</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,82</t>
+          <t>21,79</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162,26%</t>
+          <t>164,21%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,78; -3,26</t>
+          <t>-56,19; -7,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 0,28</t>
+          <t>-51,5; -1,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 18,36</t>
+          <t>-24,0; 17,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,97; 41,79</t>
+          <t>0,77; 41,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,2; -6,56</t>
+          <t>-84,93; -12,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,29; 12,89</t>
+          <t>-90,72; 5,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,78; 163,41</t>
+          <t>-78,17; 177,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 842,08</t>
+          <t>-17,37; 845,11</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-4,74</t>
+          <t>-5,01</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-17,73%</t>
+          <t>-18,58%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 1,36</t>
+          <t>-23,19; 0,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,56</t>
+          <t>-13,44; 0,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 3,31</t>
+          <t>-12,87; 2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 4,23</t>
+          <t>-13,19; 3,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 5,14</t>
+          <t>-61,33; 4,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 2,71</t>
+          <t>-47,42; 2,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-48,23; 21,07</t>
+          <t>-48,94; 16,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 21,59</t>
+          <t>-41,54; 18,13</t>
         </is>
       </c>
     </row>
